--- a/server/master-excel-files/General_BIOLOGY_Grade 9.xlsx
+++ b/server/master-excel-files/General_BIOLOGY_Grade 9.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\BIOLOGY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\teacher-year-plan-app\server\master-excel-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -303,6 +303,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -320,12 +326,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -646,52 +646,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
     </row>
     <row r="3" spans="1:41" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -798,10 +798,10 @@
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -833,7 +833,7 @@
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -865,10 +865,10 @@
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="12"/>
+      <c r="C8" s="6"/>
       <c r="D8" s="1" t="s">
         <v>38</v>
       </c>
@@ -898,10 +898,10 @@
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -933,10 +933,10 @@
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="12"/>
+      <c r="C10" s="6"/>
       <c r="D10" s="1" t="s">
         <v>38</v>
       </c>
@@ -953,7 +953,7 @@
         <v>6</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>6</v>
@@ -966,10 +966,10 @@
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="6" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -988,7 +988,7 @@
         <v>6</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>6</v>
@@ -1001,10 +1001,10 @@
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="12"/>
+      <c r="C12" s="6"/>
       <c r="D12" s="1" t="s">
         <v>39</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>6</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>6</v>
@@ -1034,10 +1034,10 @@
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -1109,9 +1109,12 @@
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E1:K1 E3:G13 H3:I47 J3:K13">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E1:K1 H13:I47 J13:K13 E13:G13">
       <formula1>"Not Started,In Progress,Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E3:K12">
+      <formula1>"Not Assigned,In Progress,Completed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
